--- a/data/trans_dic/P19D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,02</t>
+          <t>2,55; 6,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,0</t>
+          <t>8,06; 14,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 15,87</t>
+          <t>8,51; 15,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 17,82</t>
+          <t>5,01; 16,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,59</t>
+          <t>4,7; 9,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 16,46</t>
+          <t>9,46; 16,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 17,38</t>
+          <t>10,51; 17,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 9,35</t>
+          <t>1,97; 8,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,33</t>
+          <t>4,08; 7,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,22</t>
+          <t>9,5; 14,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,42</t>
+          <t>10,41; 15,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,07</t>
+          <t>4,34; 10,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,13</t>
+          <t>1,99; 5,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,14</t>
+          <t>6,53; 11,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,23</t>
+          <t>4,71; 9,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,61</t>
+          <t>4,18; 10,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,12</t>
+          <t>3,91; 8,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 14,84</t>
+          <t>9,67; 15,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 13,57</t>
+          <t>8,03; 13,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,59</t>
+          <t>3,31; 7,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,8</t>
+          <t>3,29; 6,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,66; 12,31</t>
+          <t>8,56; 12,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,52</t>
+          <t>6,96; 10,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,71</t>
+          <t>4,23; 8,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,46</t>
+          <t>4,86; 9,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 14,02</t>
+          <t>8,65; 14,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,82</t>
+          <t>5,3; 9,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,55</t>
+          <t>4,82; 9,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,37</t>
+          <t>3,79; 7,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,91</t>
+          <t>5,61; 9,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,17</t>
+          <t>4,18; 8,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,39</t>
+          <t>3,64; 6,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,78</t>
+          <t>4,81; 7,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,92</t>
+          <t>7,46; 10,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,21</t>
+          <t>5,33; 8,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,84</t>
+          <t>4,62; 7,25</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,8</t>
+          <t>5,27; 10,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 16,77</t>
+          <t>10,27; 16,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,24</t>
+          <t>8,4; 14,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 68,75</t>
+          <t>5,9; 10,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 10,02</t>
+          <t>4,89; 9,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,58</t>
+          <t>6,15; 11,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,4</t>
+          <t>4,94; 9,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,61</t>
+          <t>2,87; 5,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,19</t>
+          <t>5,79; 9,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,05</t>
+          <t>8,93; 13,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,75</t>
+          <t>7,22; 10,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 49,74</t>
+          <t>4,6; 6,95</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 16,66</t>
+          <t>8,45; 16,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,12; 22,08</t>
+          <t>14,09; 22,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,27</t>
+          <t>6,71; 12,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,62</t>
+          <t>6,9; 11,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,12</t>
+          <t>4,62; 10,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,91</t>
+          <t>6,62; 12,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 10,1</t>
+          <t>4,84; 10,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,39</t>
+          <t>4,61; 7,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,04</t>
+          <t>7,5; 12,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 16,37</t>
+          <t>11,3; 16,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,65</t>
+          <t>6,66; 10,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,44</t>
+          <t>6,29; 9,03</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 16,3</t>
+          <t>7,38; 15,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,6; 27,31</t>
+          <t>16,51; 27,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,65</t>
+          <t>7,36; 15,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,27; 13,48</t>
+          <t>8,77; 14,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,08</t>
+          <t>6,9; 14,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,74</t>
+          <t>9,03; 16,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,61</t>
+          <t>6,81; 13,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,52</t>
+          <t>6,31; 10,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,98; 13,31</t>
+          <t>7,98; 13,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,96; 20,37</t>
+          <t>13,81; 20,43</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,16</t>
+          <t>7,97; 13,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 9,81</t>
+          <t>8,1; 11,33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 22,67</t>
+          <t>8,99; 22,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,25; 32,29</t>
+          <t>18,06; 31,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,85</t>
+          <t>4,9; 12,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 14,09</t>
+          <t>7,79; 13,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 11,87</t>
+          <t>4,3; 11,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,96; 24,22</t>
+          <t>14,59; 23,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,03</t>
+          <t>7,7; 18,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,72</t>
+          <t>7,84; 11,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,06; 13,88</t>
+          <t>7,31; 14,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,38; 24,82</t>
+          <t>17,1; 25,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 14,31</t>
+          <t>7,78; 14,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,86</t>
+          <t>8,27; 11,59</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,27</t>
+          <t>6,27; 8,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,88</t>
+          <t>12,34; 15,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,49</t>
+          <t>8,12; 10,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,87; 36,7</t>
+          <t>7,56; 9,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,72</t>
+          <t>5,82; 7,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,12</t>
+          <t>9,93; 12,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,94</t>
+          <t>7,83; 9,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,22</t>
+          <t>5,19; 6,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,66</t>
+          <t>6,22; 7,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,07</t>
+          <t>11,38; 13,16</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,29; 9,73</t>
+          <t>8,31; 9,88</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,36; 21,5</t>
+          <t>6,51; 7,83</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40012</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54012</t>
+          <t>49688</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9053; 25216</t>
+          <t>9155; 23789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28707; 53212</t>
+          <t>30641; 54947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30669; 56009</t>
+          <t>30014; 54560</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20392; 67741</t>
+          <t>18839; 60497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16753; 36079</t>
+          <t>17683; 36441</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34415; 60759</t>
+          <t>34896; 60391</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37295; 61174</t>
+          <t>36978; 62928</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6253; 28215</t>
+          <t>6713; 27931</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29417; 53934</t>
+          <t>30032; 53882</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70571; 106560</t>
+          <t>71191; 107282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72227; 108685</t>
+          <t>73342; 108371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32439; 89123</t>
+          <t>31092; 78034</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47713</t>
+          <t>55041</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11718; 29628</t>
+          <t>11475; 30621</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37389; 66094</t>
+          <t>38740; 68429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22867; 45534</t>
+          <t>23221; 47479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14746; 42848</t>
+          <t>18705; 49107</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21122; 44494</t>
+          <t>21429; 44870</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51602; 83104</t>
+          <t>54159; 84284</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40277; 67389</t>
+          <t>39890; 67774</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12352; 32963</t>
+          <t>15975; 35370</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35852; 65294</t>
+          <t>37049; 67554</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99882; 141949</t>
+          <t>98675; 141341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69964; 104086</t>
+          <t>68896; 103818</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31833; 69735</t>
+          <t>39322; 75561</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31804</t>
+          <t>41480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57206</t>
+          <t>71662</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24127; 47596</t>
+          <t>24450; 48649</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49890; 82102</t>
+          <t>50666; 83310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29966; 54580</t>
+          <t>29436; 54284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21898; 44887</t>
+          <t>28881; 54607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22563; 44488</t>
+          <t>22847; 45373</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36965; 65172</t>
+          <t>36910; 64370</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23095; 46821</t>
+          <t>23947; 46571</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17776; 33976</t>
+          <t>22041; 40593</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52879; 86095</t>
+          <t>53219; 84589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93782; 135678</t>
+          <t>92693; 135458</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57999; 92679</t>
+          <t>60222; 95246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44570; 72269</t>
+          <t>55729; 87404</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287819</t>
+          <t>52496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>316207</t>
+          <t>80764</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21701; 43713</t>
+          <t>21329; 43018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56578; 90484</t>
+          <t>55448; 90313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42483; 72985</t>
+          <t>43021; 74060</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55858; 593198</t>
+          <t>40007; 68656</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21529; 44017</t>
+          <t>21456; 43017</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35717; 64998</t>
+          <t>34535; 63106</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26575; 51233</t>
+          <t>26906; 50277</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19560; 46457</t>
+          <t>20788; 37023</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48047; 77568</t>
+          <t>48838; 78821</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98931; 143641</t>
+          <t>98291; 143224</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75234; 113694</t>
+          <t>76376; 113287</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76607; 778834</t>
+          <t>64545; 97492</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45594</t>
+          <t>54096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>35301</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76376</t>
+          <t>89397</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23051; 45371</t>
+          <t>23027; 45481</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51159; 80033</t>
+          <t>51074; 80817</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25591; 49220</t>
+          <t>24904; 48169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35664; 58273</t>
+          <t>41108; 69131</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16018; 35497</t>
+          <t>14756; 34031</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25264; 50562</t>
+          <t>25930; 50847</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18517; 40000</t>
+          <t>19159; 41687</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23394; 39512</t>
+          <t>27449; 45521</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43364; 71191</t>
+          <t>44371; 72876</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83619; 123401</t>
+          <t>85228; 123678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50655; 81705</t>
+          <t>51107; 82968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63934; 91516</t>
+          <t>74987; 107611</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>44155</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>31698</t>
+          <t>34600</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69908</t>
+          <t>78755</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16080; 34824</t>
+          <t>15758; 33854</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43403; 71404</t>
+          <t>43175; 72355</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17174; 36004</t>
+          <t>16947; 36152</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29535; 48165</t>
+          <t>34670; 55327</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17119; 34769</t>
+          <t>17030; 34816</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27348; 50157</t>
+          <t>27050; 50626</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17617; 37690</t>
+          <t>18847; 38393</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11353; 51244</t>
+          <t>27180; 43608</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36749; 61301</t>
+          <t>36744; 61447</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78348; 114305</t>
+          <t>77499; 114630</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40301; 66726</t>
+          <t>40431; 67603</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36221; 94027</t>
+          <t>66938; 93562</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29291</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>43725</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>68790</t>
+          <t>75162</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12028; 28737</t>
+          <t>11394; 28518</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33755; 59707</t>
+          <t>33388; 58746</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7200; 18891</t>
+          <t>7200; 18686</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22007; 38963</t>
+          <t>23668; 41530</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7968; 24710</t>
+          <t>8963; 24734</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45542; 73749</t>
+          <t>44421; 71847</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17204; 38591</t>
+          <t>17441; 40834</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31681; 48078</t>
+          <t>35086; 53552</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23650; 46480</t>
+          <t>24476; 46911</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85074; 121466</t>
+          <t>83710; 123212</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27896; 53488</t>
+          <t>29063; 53613</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56584; 81439</t>
+          <t>62083; 87057</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>499437</t>
+          <t>289180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>190775</t>
+          <t>211289</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>690212</t>
+          <t>500469</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>151457; 203230</t>
+          <t>154159; 204118</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>355589; 432742</t>
+          <t>358780; 437270</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216888; 279167</t>
+          <t>216282; 275981</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>264103; 1231091</t>
+          <t>256671; 328757</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>159488; 211701</t>
+          <t>159527; 212697</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>310960; 381103</t>
+          <t>312089; 383088</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>224481; 284889</t>
+          <t>224495; 283527</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>153103; 222707</t>
+          <t>188175; 238187</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>327531; 397914</t>
+          <t>323118; 399839</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>685550; 790818</t>
+          <t>688484; 796289</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>458366; 538181</t>
+          <t>459685; 546080</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>441272; 1491175</t>
+          <t>457186; 550184</t>
         </is>
       </c>
     </row>
